--- a/code_mapping/[iCUBE] 7. 근태코드매핑정의서.xlsx
+++ b/code_mapping/[iCUBE] 7. 근태코드매핑정의서.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\통합\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,7 +16,6 @@
     <sheet name="예시" sheetId="11" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -52,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
   <si>
     <t>Y</t>
   </si>
@@ -307,6 +306,10 @@
       <t>[인사기초코드등록] 
 'T3' (근무시간형태구분)</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근태코드매핑정의서</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -649,7 +652,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -739,6 +742,145 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1044,184 +1186,209 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J15"/>
+  <dimension ref="B1:J16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.125" customWidth="1"/>
-    <col min="2" max="7" width="30.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="30.625" customWidth="1"/>
-    <col min="9" max="10" width="30.625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="2.125" style="51" customWidth="1"/>
+    <col min="2" max="8" width="30.625" style="60" customWidth="1"/>
+    <col min="9" max="10" width="30.625" style="62" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="4"/>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="30" t="s">
+    <row r="1" spans="2:10" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="39">
+        <v>20260513</v>
+      </c>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+    </row>
+    <row r="2" spans="2:10" s="30" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="32"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+    </row>
+    <row r="3" spans="2:10" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-    </row>
-    <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="34"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="37"/>
-    </row>
-    <row r="4" spans="2:10" s="16" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-    </row>
-    <row r="5" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="7" t="s">
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
+    </row>
+    <row r="4" spans="2:10" s="30" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="70"/>
+    </row>
+    <row r="5" spans="2:10" s="33" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" spans="2:10" s="30" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C6" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D6" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E6" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F6" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G6" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H6" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I6" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J6" s="38" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
+    <row r="7" spans="2:10" s="30" customFormat="1" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C7" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D7" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E7" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F7" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G7" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H7" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="26" t="s">
+      <c r="I7" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J7" s="43" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="29"/>
-    </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="11"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="50"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="2"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="11"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="55"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="2"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="11"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="55"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="2"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="F15" s="24" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="52"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="55"/>
+    </row>
+    <row r="13" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="56"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="59"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F16" s="61" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
-    <mergeCell ref="B2:J3"/>
+    <mergeCell ref="B3:J4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1244,28 +1411,28 @@
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="34"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="37"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="2:10" s="16" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="14"/>
@@ -1515,6 +1682,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:J3"/>
   </mergeCells>

--- a/code_mapping/[iCUBE] 7. 근태코드매핑정의서.xlsx
+++ b/code_mapping/[iCUBE] 7. 근태코드매핑정의서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\통합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="근태코드매핑정의서" sheetId="7" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
   <si>
     <t>Y</t>
   </si>
@@ -310,6 +310,10 @@
   </si>
   <si>
     <t>근태코드매핑정의서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260903</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1199,8 +1203,8 @@
       <c r="B1" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="39">
-        <v>20260513</v>
+      <c r="C1" s="39" t="s">
+        <v>50</v>
       </c>
       <c r="D1" s="39"/>
       <c r="E1" s="39"/>
@@ -1386,7 +1390,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="W0CjRrzmJlxiQ5EcADV/4SMCr+ijQo/pN8Et48CflTr5VdWzqgHZzvTwB+2vmeaaUXV80LXZjvZEv3daprbP9Q==" saltValue="tvRj+RfVclrNYJOZoN6Qmw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B3:J4"/>
   </mergeCells>
@@ -1682,7 +1686,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="82GFKPD59Fdrk6im7altpv0XBBRedHfOBt6i80WKBTFOYNRnmEMDUne621YRUMiJEqYSoewEwQgfCjeA6M/Bcg==" saltValue="Cq9+BYy/HSK+8U6xfj6+rg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:J3"/>
   </mergeCells>
